--- a/亚丰发票模板.xlsx
+++ b/亚丰发票模板.xlsx
@@ -24,475 +24,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3191" name="ID_01E5CA339D6A44BBBAE6174EC5CFEC35"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1754022400"/>
-          <a:ext cx="3419475" cy="4572000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3192" name="ID_502BD09F695545C09F03C83C96583B66"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1754352600"/>
-          <a:ext cx="3810000" cy="4724400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3190" name="ID_5FCF373CB556463AB7D539CB1C9F25F8"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1753692200"/>
-          <a:ext cx="4324350" cy="5438775"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3194" name="ID_42D672FBCF2E4A9BA73A2649FA2BEDEA"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1755013000"/>
-          <a:ext cx="3486150" cy="4581525"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3195" name="ID_170A6921BD684C6587832ED95D8DE935"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1755343200"/>
-          <a:ext cx="3524250" cy="6238875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3197" name="ID_AE0EB0ABCE2C494B82E92F053998AE75"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1756003600"/>
-          <a:ext cx="3524250" cy="6143625"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3196" name="ID_01D7FE365692407BBC8359F593625876"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1755673400"/>
-          <a:ext cx="3324225" cy="6219825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3198" name="ID_266924F60B8141299EEC3DA156EF79C8"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1756333800"/>
-          <a:ext cx="4333875" cy="6096000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3199" name="ID_CC755C7BAC854C3F906E770DA0C70766"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1756664000"/>
-          <a:ext cx="3905250" cy="6048375"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2184" name="ID_FE00294DB2664517A752B77510AC57B3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId10" r:link="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10074910" y="1530807200"/>
-          <a:ext cx="15240000" cy="19050000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3200" name="ID_0C558B95D7A243B7A5134C661B7FEFBA"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1756994200"/>
-          <a:ext cx="4229100" cy="4476750"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3201" name="ID_9F77A9B920154886A4232B997220124F"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1757324400"/>
-          <a:ext cx="4371975" cy="3886200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3163" name="ID_FC6E94C90A5F43239E0F1A3297AB9795"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1743456000"/>
-          <a:ext cx="3867150" cy="3467100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3202" name="ID_C9A08AA3806A468E92CB6E49A229ADDA"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1757654600"/>
-          <a:ext cx="4267200" cy="6191250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3203" name="ID_64BD7794553B4FA6886EDD900741F8AC"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1757984800"/>
-          <a:ext cx="4600575" cy="3190875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3170" name="ID_635D531F4A1944F7A950C6BD24AD9761"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10470515" y="1745767400"/>
-          <a:ext cx="4391025" cy="3248025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-</etc:cellImages>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1981,53 +1512,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>17780</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>635</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>348615</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>33020</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10755630" y="635"/>
-          <a:ext cx="7773670" cy="2943225"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -5895,7 +5379,6 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>